--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeilysVillalobosSequ\Downloads\t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC3C0BE-5B41-46AF-9D2E-09CDEECDDE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC03EEDD-CCCC-48BB-8A2F-D5BC2B8DFAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>nombre</t>
   </si>
@@ -32,60 +32,6 @@
   </si>
   <si>
     <t>descripcion</t>
-  </si>
-  <si>
-    <t>Cargador USB-C 65W</t>
-  </si>
-  <si>
-    <t>cargador-usb.svg</t>
-  </si>
-  <si>
-    <t>Carga rápida compatible con laptops y celulares</t>
-  </si>
-  <si>
-    <t>Audífonos Bluetooth</t>
-  </si>
-  <si>
-    <t>audifonos-bt.svg</t>
-  </si>
-  <si>
-    <t>Sonido HD, 20h de batería, cancelación de ruido</t>
-  </si>
-  <si>
-    <t>Cable HDMI 2m 4K</t>
-  </si>
-  <si>
-    <t>cable-hdmi.svg</t>
-  </si>
-  <si>
-    <t>Resolución 4K UHD, conectores dorados resistentes</t>
-  </si>
-  <si>
-    <t>Powerbank 20000mAh</t>
-  </si>
-  <si>
-    <t>powerbank.svg</t>
-  </si>
-  <si>
-    <t>Carga 3 dispositivos simultáneamente</t>
-  </si>
-  <si>
-    <t>Hub USB 7 Puertos</t>
-  </si>
-  <si>
-    <t>hub-usb.svg</t>
-  </si>
-  <si>
-    <t>Compatible USB 3.0 y 2.0, con LED indicador</t>
-  </si>
-  <si>
-    <t>Cámara</t>
-  </si>
-  <si>
-    <t>camara.jpg</t>
-  </si>
-  <si>
-    <t>Cámara Solar</t>
   </si>
 </sst>
 </file>
@@ -517,88 +463,40 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4">
-        <v>2500</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4">
-        <v>15000</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4">
-        <v>18000</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4">
-        <v>25000</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="6">
-        <v>28000</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeilysVillalobosSequ\Downloads\t\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\src\multiservicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC03EEDD-CCCC-48BB-8A2F-D5BC2B8DFAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA4E653-E517-4CF6-93C6-5C86FAE7F513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>nombre</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>descripcion</t>
+  </si>
+  <si>
+    <t>cantidad</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -448,7 +451,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,38 +464,41 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="4"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="4"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="5"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\src\multiservicios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeilysVillalobosSequ\Downloads\t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA4E653-E517-4CF6-93C6-5C86FAE7F513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512F17E8-604F-4839-AFDE-85F5B0E134F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>nombre</t>
   </si>
@@ -34,7 +34,13 @@
     <t>descripcion</t>
   </si>
   <si>
-    <t>cantidad</t>
+    <t>promocion</t>
+  </si>
+  <si>
+    <t>prod1</t>
+  </si>
+  <si>
+    <t>prod prod</t>
   </si>
 </sst>
 </file>
@@ -120,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -139,6 +145,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,15 +473,24 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="4"/>
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1000</v>
+      </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,22 +5,132 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeilysVillalobosSequ\Downloads\t\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpace\src\multiservicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512F17E8-604F-4839-AFDE-85F5B0E134F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A544CDDC-B9DE-4F96-AAC6-F3EFBB1E9406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
+    <sheet name="Banner" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Deilys Villalobos Sequeira</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{3A3251FC-C64C-4533-BA25-46845059E2D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Deilys Villalobos Sequeira:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1 activo
+2. desactivado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{3E86F9EA-584F-4079-8D42-DC13990131EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Deilys Villalobos Sequeira:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+info
+urgente
+promo</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{B921512A-A579-4DDA-9AF8-4578C5857F1F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Deilys Villalobos Sequeira:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Link opcional</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{E89E017E-2E50-4629-84B2-34ACC9F1D966}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Deilys Villalobos Sequeira:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Etiqueta del link, por defecto "Ver Más"</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nombre</t>
   </si>
@@ -41,6 +151,21 @@
   </si>
   <si>
     <t>prod prod</t>
+  </si>
+  <si>
+    <t>mensaje</t>
+  </si>
+  <si>
+    <t>activo</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>link_texto</t>
   </si>
 </sst>
 </file>
@@ -50,7 +175,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-[$₡-140A]* #,##0.00_-;\-[$₡-140A]* #,##0.00_-;_-[$₡-140A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,8 +189,28 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -87,8 +232,14 @@
         <fgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -122,11 +273,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC7D2FE"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC7D2FE"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC7D2FE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC7D2FE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC7D2FE"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC7D2FE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC7D2FE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +329,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,4 +712,35 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2375392-818D-420E-A5A3-B0B264BD9831}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>